--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,312 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120141705</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506714</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7114740</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120141695</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506750</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7114935</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120141702</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>506729</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7114816</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141705</v>
+        <v>120141695</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506714</v>
+        <v>506750</v>
       </c>
       <c r="R5" t="n">
-        <v>7114740</v>
+        <v>7114935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141695</v>
+        <v>120141702</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506750</v>
+        <v>506729</v>
       </c>
       <c r="R6" t="n">
-        <v>7114935</v>
+        <v>7114816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141702</v>
+        <v>120141705</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506729</v>
+        <v>506714</v>
       </c>
       <c r="R7" t="n">
-        <v>7114816</v>
+        <v>7114740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>120141695</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141702</v>
+        <v>120141705</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506729</v>
+        <v>506714</v>
       </c>
       <c r="R6" t="n">
-        <v>7114816</v>
+        <v>7114740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141705</v>
+        <v>120141702</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506714</v>
+        <v>506729</v>
       </c>
       <c r="R7" t="n">
-        <v>7114740</v>
+        <v>7114816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141705</v>
+        <v>120141702</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506714</v>
+        <v>506729</v>
       </c>
       <c r="R6" t="n">
-        <v>7114740</v>
+        <v>7114816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141702</v>
+        <v>120141705</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506729</v>
+        <v>506714</v>
       </c>
       <c r="R7" t="n">
-        <v>7114816</v>
+        <v>7114740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141695</v>
+        <v>120141705</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506750</v>
+        <v>506714</v>
       </c>
       <c r="R5" t="n">
-        <v>7114935</v>
+        <v>7114740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141705</v>
+        <v>120141695</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506714</v>
+        <v>506750</v>
       </c>
       <c r="R7" t="n">
-        <v>7114740</v>
+        <v>7114935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141705</v>
+        <v>120141695</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506714</v>
+        <v>506750</v>
       </c>
       <c r="R5" t="n">
-        <v>7114740</v>
+        <v>7114935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141695</v>
+        <v>120141705</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506750</v>
+        <v>506714</v>
       </c>
       <c r="R7" t="n">
-        <v>7114935</v>
+        <v>7114740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141695</v>
+        <v>120141705</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506750</v>
+        <v>506714</v>
       </c>
       <c r="R5" t="n">
-        <v>7114935</v>
+        <v>7114740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141702</v>
+        <v>120141695</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506729</v>
+        <v>506750</v>
       </c>
       <c r="R6" t="n">
-        <v>7114816</v>
+        <v>7114935</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141705</v>
+        <v>120141702</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506714</v>
+        <v>506729</v>
       </c>
       <c r="R7" t="n">
-        <v>7114740</v>
+        <v>7114816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17685-2020 artfynd.xlsx
+++ b/artfynd/A 17685-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141705</v>
+        <v>120141695</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506714</v>
+        <v>506750</v>
       </c>
       <c r="R5" t="n">
-        <v>7114740</v>
+        <v>7114935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141695</v>
+        <v>120141702</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506750</v>
+        <v>506729</v>
       </c>
       <c r="R6" t="n">
-        <v>7114935</v>
+        <v>7114816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141702</v>
+        <v>120141705</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506729</v>
+        <v>506714</v>
       </c>
       <c r="R7" t="n">
-        <v>7114816</v>
+        <v>7114740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
